--- a/\\172.25.70.143\Injaaz\General\CAFM/Daily Report on Resolved and Pending Complaints for 15th of July 2026 & 16th of July 2026.xlsx
+++ b/\\172.25.70.143\Injaaz\General\CAFM/Daily Report on Resolved and Pending Complaints for 15th of July 2026 & 16th of July 2026.xlsx
@@ -999,7 +999,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 05 Sep 2026  21:10</t>
+          <t>Generated: 05 Sep 2026  21:47</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 05 Sep 2026  21:10</t>
+          <t>Generated: 05 Sep 2026  21:47</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 05 Sep 2026  21:10</t>
+          <t>Generated: 05 Sep 2026  21:47</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 05 Sep 2026  21:10</t>
+          <t>Generated: 05 Sep 2026  21:47</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 05 Sep 2026  21:10</t>
+          <t>Generated: 05 Sep 2026  21:47</t>
         </is>
       </c>
     </row>
